--- a/sample/種の受注台帳.xlsx
+++ b/sample/種の受注台帳.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">受付日</t>
   </si>
@@ -29,6 +29,12 @@
   </si>
   <si>
     <t xml:space="preserve">金額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入金日</t>
   </si>
   <si>
     <t xml:space="preserve">発送</t>
@@ -110,6 +116,8 @@
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -137,19 +145,25 @@
       <c r="H1" t="s" s="1">
         <v>7</v>
       </c>
+      <c r="I1" t="s" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -162,21 +176,24 @@
         <v>720</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -189,7 +206,10 @@
         <v>1260</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
